--- a/SGC-CKN/Excel/de911223-0f73-4b4f-b99a-1d92e317367d_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-49_D800_16-03-2026.xlsx
+++ b/SGC-CKN/Excel/de911223-0f73-4b4f-b99a-1d92e317367d_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-49_D800_16-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="72">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P7-49</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t/>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>SGCT-KCN0004</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">03:30
@@ -106,10 +106,13 @@
 16/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">03:50
@@ -123,9 +126,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">04:03
 16/03/2026</t>
   </si>
@@ -151,7 +151,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">07:00
@@ -165,9 +165,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">07:53
 16/03/2026</t>
   </si>
@@ -179,7 +176,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:00
@@ -189,7 +186,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1. Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:50
@@ -199,9 +196,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">15:30
 16/03/2026</t>
   </si>
@@ -209,7 +203,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đá màu sắc TT rất chặt</t>
+    <t>Cuội, sỏi, sạn cát, đá khoảng, đa sắc, TT chặt đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:10
@@ -257,7 +251,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -328,18 +322,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF831843"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF134E4A"/>
+      <color rgb="FF831843"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -356,7 +345,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -430,17 +419,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99F6E4"/>
+        <fgColor rgb="FFFBCFE8"/>
       </patternFill>
     </fill>
     <fill>
@@ -536,7 +520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -631,31 +615,22 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1256,24 +1231,24 @@
         <v>17.43</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-6.54</v>
@@ -1291,18 +1266,18 @@
         <v>15.05</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>36</v>
@@ -1326,7 +1301,7 @@
         <v>4.87</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1361,7 +1336,7 @@
         <v>2.84</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1396,198 +1371,198 @@
         <v>7.31</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="E16" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="22">
+      <c r="F16" s="19">
         <v>-28</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="19">
         <v>-35</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="19">
         <v>2.45</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="19">
         <v>7</v>
       </c>
       <c r="J16" s="15">
         <v>2.86</v>
       </c>
-      <c r="K16" s="23" t="s">
-        <v>9</v>
+      <c r="K16" s="20" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="D17" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="F17" s="22">
         <v>-35</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="22">
         <v>-37.5</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="22">
         <v>0.67</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="22">
         <v>2.5</v>
       </c>
       <c r="J17" s="15">
         <v>3.75</v>
       </c>
-      <c r="K17" s="26" t="s">
-        <v>9</v>
+      <c r="K17" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="28">
+      <c r="F18" s="25">
         <v>-37.5</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="25">
         <v>-39</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="25">
         <v>0.83</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="25">
         <v>1.5</v>
       </c>
       <c r="J18" s="15">
         <v>1.8</v>
       </c>
-      <c r="K18" s="29" t="s">
-        <v>9</v>
+      <c r="K18" s="26" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="F19" s="28">
+        <v>-39</v>
+      </c>
+      <c r="G19" s="28">
+        <v>-42.2</v>
+      </c>
+      <c r="H19" s="28">
+        <v>3.67</v>
+      </c>
+      <c r="I19" s="28">
+        <v>3.2</v>
+      </c>
+      <c r="J19" s="31">
+        <v>0.87</v>
+      </c>
+      <c r="K19" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="33" t="s">
+      <c r="C20" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="F19" s="31">
-        <v>-39</v>
-      </c>
-      <c r="G19" s="31">
+      <c r="D20" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="32">
         <v>-42.2</v>
       </c>
-      <c r="H19" s="31">
-        <v>3.67</v>
-      </c>
-      <c r="I19" s="31">
-        <v>3.2</v>
-      </c>
-      <c r="J19" s="34">
-        <v>0.87</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="35">
-        <v>-42.2</v>
-      </c>
-      <c r="G20" s="35">
+      <c r="G20" s="32">
         <v>-44.89</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="32">
         <v>1.33</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="32">
         <v>2.69</v>
       </c>
       <c r="J20" s="15">
         <v>2.02</v>
       </c>
-      <c r="K20" s="36" t="s">
-        <v>63</v>
+      <c r="K20" s="33" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="A23" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1669,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1682,31 +1657,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1746,7 +1721,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1775,7 +1750,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1836,22 +1811,22 @@
         <v>43</v>
       </c>
       <c r="D6" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="19">
         <v>-21.3</v>
       </c>
       <c r="F6" s="19">
-        <v>-28</v>
+        <v>-35</v>
       </c>
       <c r="G6" s="19">
-        <v>0.92</v>
+        <v>3.37</v>
       </c>
       <c r="H6" s="19">
-        <v>6.7</v>
-      </c>
-      <c r="I6" s="8">
-        <v>7.31</v>
+        <v>13.7</v>
+      </c>
+      <c r="I6" s="15">
+        <v>4.07</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1862,25 +1837,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-28</v>
+        <v>-35</v>
       </c>
       <c r="F7" s="22">
-        <v>-35</v>
+        <v>-37.5</v>
       </c>
       <c r="G7" s="22">
-        <v>2.45</v>
+        <v>0.67</v>
       </c>
       <c r="H7" s="22">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="I7" s="15">
-        <v>2.86</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1891,25 +1866,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-35</v>
+        <v>-37.5</v>
       </c>
       <c r="F8" s="25">
-        <v>-37.5</v>
+        <v>-39</v>
       </c>
       <c r="G8" s="25">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="H8" s="25">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="I8" s="15">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1920,111 +1895,82 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-37.5</v>
+        <v>-39</v>
       </c>
       <c r="F9" s="28">
-        <v>-39</v>
+        <v>-42.2</v>
       </c>
       <c r="G9" s="28">
-        <v>0.83</v>
+        <v>3.67</v>
       </c>
       <c r="H9" s="28">
-        <v>1.5</v>
-      </c>
-      <c r="I9" s="15">
-        <v>1.8</v>
+        <v>3.2</v>
+      </c>
+      <c r="I9" s="31">
+        <v>0.87</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="31">
+      <c r="A10" s="32">
         <v>9</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="31">
+      <c r="C10" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="32">
         <v>1</v>
       </c>
-      <c r="E10" s="31">
-        <v>-39</v>
-      </c>
-      <c r="F10" s="31">
+      <c r="E10" s="32">
         <v>-42.2</v>
       </c>
-      <c r="G10" s="31">
-        <v>3.67</v>
-      </c>
-      <c r="H10" s="31">
-        <v>3.2</v>
-      </c>
-      <c r="I10" s="34">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="F10" s="32">
+        <v>-44.89</v>
+      </c>
+      <c r="G10" s="32">
+        <v>1.33</v>
+      </c>
+      <c r="H10" s="32">
+        <v>2.69</v>
+      </c>
+      <c r="I10" s="15">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="37">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="35">
-        <v>1</v>
-      </c>
-      <c r="E11" s="35">
-        <v>-42.2</v>
-      </c>
-      <c r="F11" s="35">
+      <c r="E11" s="37">
+        <v>-1.02</v>
+      </c>
+      <c r="F11" s="37">
         <v>-44.89</v>
       </c>
-      <c r="G11" s="35">
-        <v>1.33</v>
-      </c>
-      <c r="H11" s="35">
-        <v>2.69</v>
-      </c>
-      <c r="I11" s="15">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="40">
-        <v>10</v>
-      </c>
-      <c r="E12" s="40">
-        <v>-1.02</v>
-      </c>
-      <c r="F12" s="40">
-        <v>-44.89</v>
-      </c>
-      <c r="G12" s="40">
+      <c r="G11" s="37">
         <v>13.32</v>
       </c>
-      <c r="H12" s="40">
+      <c r="H11" s="37">
         <v>43.87</v>
       </c>
-      <c r="I12" s="40">
+      <c r="I11" s="37">
         <v>3.29</v>
       </c>
     </row>
